--- a/data/trans_bre/IP15-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 12,17</t>
+          <t>-2,52; 12,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 8,86</t>
+          <t>-7,94; 8,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 9,97</t>
+          <t>-6,75; 9,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 12,44</t>
+          <t>-6,77; 11,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 78,76</t>
+          <t>-11,55; 82,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 48,15</t>
+          <t>-30,79; 48,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 77,01</t>
+          <t>-31,91; 79,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 86,18</t>
+          <t>-28,11; 72,45</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 7,78</t>
+          <t>-4,24; 8,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 7,98</t>
+          <t>-3,9; 9,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 7,88</t>
+          <t>-3,8; 8,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 7,15</t>
+          <t>-9,58; 6,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 47,32</t>
+          <t>-19,48; 55,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 53,61</t>
+          <t>-18,25; 62,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 50,81</t>
+          <t>-18,18; 54,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 32,34</t>
+          <t>-34,61; 30,71</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 2,24</t>
+          <t>-12,57; 2,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 6,68</t>
+          <t>-8,06; 6,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 7,85</t>
+          <t>-4,7; 8,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 36,86</t>
+          <t>-3,81; 34,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 11,14</t>
+          <t>-45,07; 14,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 35,73</t>
+          <t>-31,28; 37,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 59,93</t>
+          <t>-24,47; 61,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 147,63</t>
+          <t>-12,24; 135,14</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,32; -0,06</t>
+          <t>-12,62; -0,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 4,25</t>
+          <t>-10,63; 3,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 7,04</t>
+          <t>-4,78; 7,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 6,79</t>
+          <t>-7,0; 6,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,6; -1,38</t>
+          <t>-56,96; -5,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 21,8</t>
+          <t>-39,65; 20,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 61,75</t>
+          <t>-27,15; 69,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 47,22</t>
+          <t>-32,16; 47,11</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,55</t>
+          <t>-4,73; 1,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,41</t>
+          <t>-3,8; 3,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,82</t>
+          <t>-1,8; 5,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 13,14</t>
+          <t>-2,23; 12,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 8,31</t>
+          <t>-21,96; 9,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 17,62</t>
+          <t>-16,67; 18,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 32,24</t>
+          <t>-10,0; 35,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 55,73</t>
+          <t>-8,96; 58,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 12,49</t>
+          <t>-2,57; 13,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 8,77</t>
+          <t>-7,51; 8,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 9,71</t>
+          <t>-5,83; 9,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 11,44</t>
+          <t>-6,34; 12,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 82,67</t>
+          <t>-12,67; 88,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,79; 48,78</t>
+          <t>-29,56; 48,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 79,3</t>
+          <t>-30,43; 73,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 72,45</t>
+          <t>-25,71; 81,14</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 8,69</t>
+          <t>-4,45; 8,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 9,5</t>
+          <t>-3,81; 8,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 8,48</t>
+          <t>-3,83; 8,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 6,89</t>
+          <t>-8,76; 7,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 55,71</t>
+          <t>-19,92; 52,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 62,5</t>
+          <t>-18,2; 55,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 54,26</t>
+          <t>-18,24; 56,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 30,71</t>
+          <t>-32,15; 34,72</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 2,24</t>
+          <t>-11,4; 2,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 6,61</t>
+          <t>-8,18; 6,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 8,07</t>
+          <t>-5,77; 8,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 34,2</t>
+          <t>-3,1; 34,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,07; 14,83</t>
+          <t>-43,42; 12,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 37,41</t>
+          <t>-32,19; 34,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 61,72</t>
+          <t>-29,98; 65,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 135,14</t>
+          <t>-10,41; 141,57</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,62; -0,79</t>
+          <t>-12,14; -0,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 3,88</t>
+          <t>-9,77; 4,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 7,56</t>
+          <t>-4,67; 6,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 6,77</t>
+          <t>-7,28; 5,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,96; -5,22</t>
+          <t>-56,7; -5,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 20,54</t>
+          <t>-36,6; 22,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 69,94</t>
+          <t>-27,05; 61,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 47,11</t>
+          <t>-31,71; 39,39</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,72</t>
+          <t>-4,82; 1,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,59</t>
+          <t>-3,73; 3,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,2</t>
+          <t>-2,02; 4,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 12,9</t>
+          <t>-2,81; 12,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 9,04</t>
+          <t>-22,21; 9,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 18,49</t>
+          <t>-16,39; 15,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 35,2</t>
+          <t>-10,74; 29,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 58,18</t>
+          <t>-10,98; 57,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 13,13</t>
+          <t>-3,12; 12,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 8,86</t>
+          <t>-7,64; 8,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 9,22</t>
+          <t>-5,01; 9,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 12,05</t>
+          <t>-6,61; 11,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 88,09</t>
+          <t>-14,29; 78,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 48,46</t>
+          <t>-30,72; 48,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,43; 73,17</t>
+          <t>-26,84; 77,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 81,14</t>
+          <t>-25,97; 86,86</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-4,27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,44%</t>
+          <t>-17,89%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 8,28</t>
+          <t>-4,76; 7,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 8,36</t>
+          <t>-3,75; 7,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 8,55</t>
+          <t>-3,83; 7,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 7,53</t>
+          <t>-11,3; 2,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 52,44</t>
+          <t>-20,67; 47,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 55,85</t>
+          <t>-17,54; 53,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 56,72</t>
+          <t>-17,7; 50,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 34,72</t>
+          <t>-41,95; 12,53</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,7</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 2,63</t>
+          <t>-12,69; 2,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 6,32</t>
+          <t>-8,79; 6,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 8,26</t>
+          <t>-5,12; 7,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 34,76</t>
+          <t>-7,75; 11,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 12,63</t>
+          <t>-47,31; 11,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 34,16</t>
+          <t>-33,61; 35,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 65,16</t>
+          <t>-27,08; 59,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 141,57</t>
+          <t>-22,03; 43,37</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-2,46%</t>
+          <t>-4,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,14; -0,99</t>
+          <t>-12,32; -0,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 4,23</t>
+          <t>-9,44; 4,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 6,9</t>
+          <t>-4,2; 7,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 5,88</t>
+          <t>-7,71; 6,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,7; -5,9</t>
+          <t>-56,6; -1,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 22,19</t>
+          <t>-35,96; 21,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 61,73</t>
+          <t>-25,48; 61,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 39,39</t>
+          <t>-35,18; 41,16</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>-3,34%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,75</t>
+          <t>-5,16; 1,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 3,14</t>
+          <t>-3,67; 3,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,51</t>
+          <t>-1,48; 4,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 12,94</t>
+          <t>-5,06; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 9,43</t>
+          <t>-23,38; 8,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 15,78</t>
+          <t>-16,33; 17,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 29,52</t>
+          <t>-8,09; 32,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 57,91</t>
+          <t>-19,07; 15,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,93</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.925116515843434</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.3110255555929087</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.891324047563905</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.173548570546449</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2629308974177494</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.01397600927444699</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1158397615325715</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1111476182227087</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,12; 12,17</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,64; 8,86</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,01; 9,97</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,61; 11,77</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-14,29; 78,76</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-30,72; 48,15</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-26,84; 77,01</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-25,97; 86,86</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.11509322449712</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.63622890970036</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.009250387505792</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.614190942704001</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1429324761702688</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3071914467816757</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2683592005618787</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2597409819947522</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.17371345460818</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.85618004001488</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.97278364570284</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.7703421728592</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.7875698467206291</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.4814946151223949</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.7701455373272326</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.8685884602874322</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,1</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,26</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,27</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-17,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,76; 7,78</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,75; 7,98</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,83; 7,88</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,3; 2,33</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-20,67; 47,32</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-17,54; 53,61</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-17,7; 50,81</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-41,95; 12,53</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.868465382584397</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.099575540235904</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.263120019737322</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-4.268136584541132</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.09596201836242219</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1165581842976419</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1233998429803298</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1788587188249172</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,21</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-22,2%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-3,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.764233918306386</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.753126963819294</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.830529707189365</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.29867374335008</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2067174787123511</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1753896407306494</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1769661444730757</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4194695186760994</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-12,69; 2,24</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,79; 6,68</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,12; 7,85</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,75; 11,28</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-47,31; 11,14</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-33,61; 35,73</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-27,08; 59,93</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-22,03; 43,37</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.781947341521233</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.978605380428213</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.877696330269784</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.332150644642168</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.4732211764607296</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.536148448391099</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.5080801805163843</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1252662868559709</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-6,41</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,96</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-34,32%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-12,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-4,43%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.209963299852105</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.7550465515841487</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.019112739259703</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.619022723405866</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2219959040888857</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.03436616275677297</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.06108633217310475</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.0520574457094144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-12,32; -0,06</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-9,44; 4,25</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,2; 7,04</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,71; 6,12</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-56,6; -1,38</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-35,96; 21,8</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-25,48; 61,75</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-35,18; 41,16</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-12.69362392513274</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.792388985592588</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.123532708005649</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.750208827742568</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4731456548498099</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3361453765663095</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.2707612239964113</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2202960373034241</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.238153148203539</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.682720002093831</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.849054830061098</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.28015496122094</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1114163191577366</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3573233704688783</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5992638376097628</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.4336669370857981</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-6.410446823237084</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.95754755606156</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.154559547361805</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.8250629360317702</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3432147319021483</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1295613863234863</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.0787938368192055</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.04433943886472605</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-12.31773750653079</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-9.443967509711786</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.197211084752025</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-7.714770091415712</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5659803050926185</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3595777428274448</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2548181847152557</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3517949906422015</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.06443144342451025</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.251653164813597</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.036184032161191</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.116529441857636</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.01381440887740116</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.218034391455106</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.6175359793831331</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.4116174092570214</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,6%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,54%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-3,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 1,55</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; 3,41</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,48; 4,82</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-5,06; 3,21</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-23,38; 8,31</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-16,33; 17,62</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-8,09; 32,24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-19,07; 15,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.514437309679839</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.3245011576576418</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.54513693779936</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.7866723337066284</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.07604862347984856</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.01538887975729601</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.09335851419593136</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.03339386391292328</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.162714120891358</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.672013901096685</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.476697057000417</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5.057411194845664</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2338327333113071</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1633162595385603</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.08089991387708446</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1907488236076569</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.551920647295891</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.408520049708221</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.817980716713777</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.206052157279022</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.08308181202454276</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1762052422905753</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.3224405682661183</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1507688055081483</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
